--- a/business_forms/026_maintenance_contract_extension_form--business_forms.xlsx
+++ b/business_forms/026_maintenance_contract_extension_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>extension_type</t>
+          <t>extension_type_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Extension Type</t>
+          <t>Extension Type 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>contract_extension_date</t>
+          <t>contract_extension_date_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Contract Extension Date</t>
+          <t>Contract Extension Date 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>contract_id</t>
+          <t>contract_id_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Contract ID</t>
+          <t>Contract Id 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Contract Extension Terms</t>
+          <t>Extension Terms</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>contract_duration</t>
+          <t>contract_duration_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Contract Duration</t>
+          <t>Contract Duration 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>contract_status</t>
+          <t>contract_status_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Contract Status</t>
+          <t>Contract Status 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>extension_reason</t>
+          <t>extension_reason_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Extension Reason</t>
+          <t>Extension Reason 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>contract_extension_terms</t>
+          <t>contract_extension_terms_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Contract Extension Terms</t>
+          <t>Contract Extension Terms 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>contract_number</t>
+          <t>contract_number_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Contract Number</t>
+          <t>Contract Number 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1101,9 +1101,9 @@
   <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'renewal'}</t>
+          <t>renewal</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Renewal'}</t>
+          <t>Renewal</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'non-renewal'}</t>
+          <t>non-renewal</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Non-Renewal'}</t>
+          <t>Non-Renewal</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'inactive'}</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Inactive'}</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
@@ -1199,97 +1199,97 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'cancelled'}</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Cancelled'}</t>
+          <t>Cancelled</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>extension_type_choices</t>
+          <t>extension_type_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'renewal'}</t>
+          <t>renewal</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Renewal'}</t>
+          <t>Renewal</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>extension_type_choices</t>
+          <t>extension_type_2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'non-renewal'}</t>
+          <t>non-renewal</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Non-Renewal'}</t>
+          <t>Non-Renewal</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>contract_status_choices</t>
+          <t>contract_status_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>contract_status_choices</t>
+          <t>contract_status_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'inactive'}</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Inactive'}</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>contract_status_choices</t>
+          <t>contract_status_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'cancelled'}</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Cancelled'}</t>
+          <t>Cancelled</t>
         </is>
       </c>
     </row>
